--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -799,7 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -1905,8 +1905,16 @@
           <t>LP08013</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Clay Loam</t>
+        </is>
+      </c>
       <c r="E45" t="n">
         <v>1.271</v>
       </c>
@@ -1942,8 +1950,16 @@
           <t xml:space="preserve">LP08004 </t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Clay Loam</t>
+        </is>
+      </c>
       <c r="E46" t="n">
         <v>3.184</v>
       </c>
@@ -1979,8 +1995,16 @@
           <t>LP08012</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Clay Loam</t>
+        </is>
+      </c>
       <c r="E47" t="n">
         <v>1.503</v>
       </c>

--- a/data/field_polygons.xlsx
+++ b/data/field_polygons.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -799,7 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -1895,14 +1895,10 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>DCGL-1791271668719-6U0260C1</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LP08013</t>
+          <t>LP08000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1912,15 +1908,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Clay Loam</t>
+          <t>Sandy Loam</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.271</v>
+        <v>30.83</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 438, "area_m2": 12713.208984375, "area_ha": 1.2713208984375, "perimeter_m": 691.2048707085324, "survey_distance_m": 689.7438334772668, "best_accuracy_m": 3, "worst_accuracy_m": 3.5450000762939453, "average_accuracy_m": 3.0320936071273943, "survey_started": "2026-10-06T07:20:37.313Z", "survey_completed": "2026-10-06T07:27:48.680Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.15892, -12.582045], [34.15893, -12.582025], [34.158936, -12.582009], [34.158942, -12.581996], [34.158946, -12.581988], [34.158954, -12.581973], [34.158962, -12.58196], [34.15897, -12.581948], [34.158978, -12.581933], [34.158986, -12.58192], [34.158991, -12.581912], [34.158999, -12.5819], [34.159004, -12.581892], [34.159012, -12.581876], [34.159019, -12.581863], [34.159025, -12.581851], [34.159033, -12.581836], [34.15904, -12.581824], [34.159049, -12.581809], [34.159056, -12.581796], [34.159063, -12.581782], [34.159071, -12.581768], [34.159079, -12.581754], [34.159087, -12.58174], [34.159095, -12.581727], [34.159102, -12.581713], [34.159111, -12.581699], [34.159119, -12.581685], [34.159127, -12.581672], [34.159133, -12.581659], [34.15914, -12.581647], [34.159148, -12.581635], [34.159153, -12.581627], [34.159162, -12.581615], [34.15917, -12.581602], [34.159177, -12.581589], [34.159184, -12.581576], [34.159193, -12.58156], [34.159198, -12.581548], [34.159204, -12.581535], [34.159208, -12.581527], [34.159216, -12.581514], [34.159224, -12.5815], [34.159233, -12.581487], [34.159242, -12.581473], [34.159249, -12.58146], [34.159255, -12.581447], [34.159262, -12.581432], [34.15927, -12.581418], [34.159277, -12.581407], [34.159283, -12.581398], [34.15929, -12.581386], [34.159295, -12.581377], [34.159303, -12.581364], [34.159312, -12.581349], [34.15932, -12.581336], [34.159329, -12.581322], [34.159338, -12.581309], [34.159345, -12.581296], [34.159352, -12.581282], [34.159359, -12.581269], [34.159364, -12.58126], [34.159371, -12.581245], [34.159377, -12.581232], [34.159381, -12.581224], [34.159389, -12.581212], [34.159397, -12.581198], [34.159404, -12.581184], [34.15941, -12.581172], [34.159415, -12.581163], [34.159422, -12.581149], [34.159428, -12.581136], [34.159432, -12.581127], [34.159439, -12.581113], [34.159448, -12.5811], [34.159455, -12.581088], [34.159464, -12.581074], [34.159472, -12.581062], [34.159481, -12.581047], [34.159486, -12.581039], [34.159491, -12.581028], [34.159496, -12.58102], [34.159505, -12.581007], [34.159513, -12.580994], [34.159521, -12.580983], [34.159531, -12.580969], [34.15954, -12.580955], [34.159547, -12.580942], [34.159555, -12.580928], [34.159562, -12.580915], [34.159569, -12.5809], [34.159573, -12.580891], [34.159579, -12.580878], [34.159586, -12.580864], [34.159592, -12.580851], [34.159599, -12.580839], [34.159606, -12.580825], [34.159615, -12.580811], [34.159624, -12.580796], [34.159632, -12.580783], [34.159637, -12.580775], [34.159644, -12.58076], [34.159651, -12.580745], [34.15966, -12.58073], [34.159669, -12.580714], [34.159678, -12.580699], [34.159686, -12.580685], [34.159696, -12.580669], [34.159702, -12.58066], [34.159709, -12.580646], [34.159714, -12.580638], [34.159721, -12.580625], [34.15973, -12.580609], [34.15974, -12.580593], [34.159751, -12.580574], [34.159756, -12.580565], [34.159764, -12.580549], [34.159772, -12.580535], [34.15978, -12.580521], [34.159788, -12.580507], [34.159795, -12.580494], [34.1598, -12.580484], [34.159804, -12.580476], [34.159812, -12.58046], [34.15982, -12.580446], [34.159829, -12.580431], [34.159836, -12.580415], [34.159843, -12.580399], [34.159849, -12.580385], [34.159856, -12.580371], [34.159864, -12.580356], [34.159872, -12.580343], [34.15988, -12.580329], [34.159889, -12.580314], [34.159898, -12.580295], [34.159903, -12.580285], [34.15991, -12.58027], [34.159917, -12.580256], [34.159925, -12.580241], [34.159932, -12.580228], [34.159941, -12.580212], [34.159949, -12.580199], [34.159957, -12.580187], [34.159965, -12.580172], [34.159973, -12.580157], [34.159981, -12.580144], [34.15999, -12.580128], [34.160002, -12.58011], [34.160009, -12.580099], [34.160018, -12.580086], [34.160026, -12.580072], [34.160032, -12.580064], [34.160039, -12.580054], [34.160045, -12.580044], [34.160053, -12.58003], [34.16006, -12.580016], [34.160067, -12.580004], [34.160072, -12.579994], [34.160079, -12.579981], [34.160083, -12.579973], [34.16009, -12.57996], [34.1601, -12.579945], [34.160108, -12.579932], [34.160113, -12.579923], [34.16012, -12.579908], [34.160127, -12.579896], [34.160131, -12.579888], [34.160143, -12.579879], [34.160158, -12.579884], [34.160173, -12.579892], [34.160189, -12.5799], [34.160204, -12.579907], [34.160219, -12.579913], [34.160236, -12.57992], [34.160253, -12.579926], [34.16027, -12.579931], [34.160289, -12.579938], [34.160298, -12.579942], [34.160312, -12.579947], [34.160328, -12.579953], [34.160342, -12.579957], [34.160357, -12.579961], [34.160373, -12.579965], [34.160383, -12.579968], [34.160393, -12.579971], [34.160403, -12.579974], [34.160418, -12.579979], [34.160435, -12.579986], [34.16045, -12.579991], [34.160458, -12.579996], [34.160472, -12.580001], [34.160486, -12.580007], [34.160491, -12.580025], [34.160485, -12.58004], [34.160475, -12.580053], [34.160466, -12.580062], [34.160455, -12.580076], [34.160449, -12.580083], [34.16044, -12.580095], [34.160431, -12.580111], [34.160424, -12.580127], [34.160416, -12.580142], [34.160407, -12.580158], [34.160398, -12.580172], [34.160394, -12.58018], [34.160386, -12.580193], [34.160378, -12.580207], [34.160369, -12.580221], [34.16036, -12.580235], [34.160352, -12.580247], [34.160344, -12.58026], [34.160337, -12.580273], [34.160329, -12.580287], [34.160322, -12.580301], [34.160314, -12.580314], [34.160307, -12.580328], [34.1603, -12.580342], [34.160291, -12.580357], [34.160284, -12.580368], [34.16028, -12.580377], [34.160273, -12.58039], [34.160267, -12.580401], [34.160263, -12.58041], [34.160255, -12.580424], [34.160247, -12.580437], [34.160239, -12.580451], [34.160233, -12.580464], [34.160226, -12.580478], [34.160219, -12.580492], [34.160213, -12.580505], [34.160206, -12.580518], [34.160199, -12.58053], [34.160191, -12.580543], [34.160186, -12.58055], [34.160177, -12.580564], [34.160173, -12.580572], [34.160165, -12.580585], [34.160159, -12.580599], [34.160152, -12.580612], [34.160143, -12.580626], [34.160136, -12.580639], [34.160129, -12.580654], [34.160122, -12.580668], [34.160115, -12.580681], [34.160109, -12.580693], [34.160104, -12.580702], [34.160098, -12.580713], [34.160091, -12.580725], [34.160086, -12.580735], [34.160078, -12.580747], [34.160072, -12.580759], [34.160063, -12.580773], [34.160055, -12.580787], [34.160048, -12.5808], [34.160044, -12.580808], [34.160037, -12.580823], [34.160029, -12.580835], [34.160021, -12.580849], [34.160014, -12.580861], [34.160009, -12.580874], [34.160005, -12.580883], [34.16, -12.580898], [34.159992, -12.58091], [34.159984, -12.580922], [34.159975, -12.580935], [34.159968, -12.580948], [34.15996, -12.580961], [34.159955, -12.580971], [34.15995, -12.580979], [34.159943, -12.580992], [34.159938, -12.581001], [34.159931, -12.581013], [34.159922, -12.581026], [34.159914, -12.581038], [34.159907, -12.581049], [34.159901, -12.581057], [34.159894, -12.581068], [34.15989, -12.581077], [34.159884, -12.58109], [34.159879, -12.581101], [34.159874, -12.581111], [34.159868, -12.581123], [34.159861, -12.581135], [34.159854, -12.581148], [34.159849, -12.581157], [34.15984, -12.581171], [34.159833, -12.581184], [34.159827, -12.581197], [34.159821, -12.581209], [34.159816, -12.581218], [34.159809, -12.581232], [34.159802, -12.581245], [34.159794, -12.581258], [34.159788, -12.58127], [34.159784, -12.581278], [34.159777, -12.58129], [34.159769, -12.581302], [34.159763, -12.581314], [34.159756, -12.581326], [34.159748, -12.581337], [34.159741, -12.581347], [34.159735, -12.581356], [34.159728, -12.581368], [34.159721, -12.58138], [34.159715, -12.581392], [34.15971, -12.5814], [34.159704, -12.581414], [34.159697, -12.581427], [34.159688, -12.581443], [34.159681, -12.581454], [34.159673, -12.581467], [34.159666, -12.581483], [34.159663, -12.581492], [34.159657, -12.581505], [34.15965, -12.581518], [34.159643, -12.58153], [34.159637, -12.581542], [34.159632, -12.581551], [34.159624, -12.581564], [34.159617, -12.581577], [34.15961, -12.581589], [34.159606, -12.581598], [34.159598, -12.581611], [34.159591, -12.581625], [34.159585, -12.581635], [34.159579, -12.581646], [34.159575, -12.581655], [34.159568, -12.581668], [34.15956, -12.581681], [34.159552, -12.581692], [34.159545, -12.581702], [34.159539, -12.581713], [34.159531, -12.581726], [34.159523, -12.581739], [34.159516, -12.581752], [34.159508, -12.581764], [34.159502, -12.581775], [34.159495, -12.581788], [34.159487, -12.581803], [34.159482, -12.581812], [34.159475, -12.581824], [34.159468, -12.581835], [34.159463, -12.581844], [34.159455, -12.581856], [34.159446, -12.581867], [34.159439, -12.581877], [34.159433, -12.581889], [34.159427, -12.581897], [34.15942, -12.581909], [34.159413, -12.581922], [34.159405, -12.581935], [34.159398, -12.581946], [34.159392, -12.581954], [34.159385, -12.581968], [34.159378, -12.581981], [34.159372, -12.581994], [34.159365, -12.582005], [34.15936, -12.582013], [34.159353, -12.582025], [34.159348, -12.582037], [34.159344, -12.582046], [34.159337, -12.582058], [34.159331, -12.582071], [34.159324, -12.582084], [34.159317, -12.582097], [34.15931, -12.582108], [34.1593, -12.582123], [34.159293, -12.582133], [34.159285, -12.582146], [34.159279, -12.582159], [34.159273, -12.582173], [34.159266, -12.582182], [34.159259, -12.582191], [34.159251, -12.582204], [34.15924, -12.582222], [34.159235, -12.58223], [34.159228, -12.582242], [34.159223, -12.582255], [34.159218, -12.582266], [34.159214, -12.582275], [34.159207, -12.582289], [34.1592, -12.582298], [34.159193, -12.582307], [34.159187, -12.582316], [34.159179, -12.582325], [34.159172, -12.582336], [34.159168, -12.582345], [34.159161, -12.582357], [34.159154, -12.582369], [34.159147, -12.58238], [34.159142, -12.582389], [34.159137, -12.582401], [34.159129, -12.582414], [34.159122, -12.582426], [34.159116, -12.582436], [34.159108, -12.582451], [34.159105, -12.582463], [34.159097, -12.582475], [34.159089, -12.582486], [34.159079, -12.582496], [34.159066, -12.582494], [34.159058, -12.582484], [34.159055, -12.582474], [34.159051, -12.582462], [34.159049, -12.582447], [34.159047, -12.582437], [34.159045, -12.582427], [34.159041, -12.582411], [34.159037, -12.582393], [34.159034, -12.582377], [34.159029, -12.582362], [34.159025, -12.582347], [34.159021, -12.582332], [34.159016, -12.582319], [34.159013, -12.58231], [34.159007, -12.582295], [34.159002, -12.582283], [34.158997, -12.582269], [34.158991, -12.582257], [34.158986, -12.582245], [34.158982, -12.582234], [34.158977, -12.582221], [34.158972, -12.582209], [34.158967, -12.582197], [34.158963, -12.582187], [34.158957, -12.582174], [34.158953, -12.582164], [34.15895, -12.582154], [34.158945, -12.582141], [34.15894, -12.582128], [34.158935, -12.582115], [34.15893, -12.582101], [34.158925, -12.582088], [34.15892, -12.582076], [34.158916, -12.582063], [34.158912, -12.582054], [34.158918, -12.582045], [34.158931, -12.582037], [34.15892, -12.582045]]]}}</t>
+          <t>{"type": "FeatureCollection", "features": [{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.156353, -12.583045], [34.15631, -12.582945], [34.156342, -12.582018], [34.156332, -12.581908], [34.156476, -12.581557], [34.156686, -12.581143], [34.156938, -12.580729], [34.157614, -12.580164], [34.15807, -12.57997], [34.158542, -12.579771], [34.159556, -12.579703], [34.160602, -12.580006], [34.160763, -12.580179], [34.161326, -12.580609], [34.161793, -12.581279], [34.162136, -12.582196], [34.16205, -12.583348], [34.161675, -12.584103], [34.161042, -12.584758], [34.160446, -12.58515], [34.159878, -12.585381], [34.159159, -12.585276], [34.158435, -12.585203], [34.157839, -12.585004], [34.157201, -12.584553], [34.156873, -12.584239], [34.156766, -12.584077], [34.156535, -12.583642], [34.156353, -12.583045]]]}}]}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1928,106 +1924,8 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-10-19 12:13</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>DCGL-1791272406563-QM3986XD</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LP08004 </t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>N41</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Clay Loam</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>3.184</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 526, "area_m2": 31836.6298828125, "area_ha": 3.18366298828125, "perimeter_m": 770.2280649640053, "survey_distance_m": 769.4484575265013, "best_accuracy_m": 3, "worst_accuracy_m": 4.191999912261963, "average_accuracy_m": 3.0290152124578964, "survey_started": "2026-10-06T07:31:10.824Z", "survey_completed": "2026-10-06T07:40:06.530Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.158919, -12.58205], [34.158919, -12.58204], [34.15892, -12.582024], [34.158926, -12.581995], [34.158928, -12.581981], [34.158941, -12.581978], [34.158955, -12.581968], [34.158963, -12.581956], [34.15897, -12.581943], [34.158977, -12.581931], [34.158984, -12.581919], [34.158992, -12.581908], [34.159001, -12.581897], [34.15901, -12.581886], [34.159019, -12.581876], [34.159027, -12.581867], [34.159034, -12.581859], [34.159042, -12.581847], [34.159048, -12.581837], [34.159053, -12.581827], [34.159059, -12.581815], [34.159066, -12.581801], [34.159072, -12.581787], [34.159079, -12.581774], [34.159083, -12.581765], [34.159089, -12.581754], [34.159096, -12.58174], [34.159104, -12.581727], [34.159112, -12.581715], [34.15912, -12.581702], [34.159127, -12.581688], [34.159134, -12.581675], [34.159141, -12.581663], [34.159149, -12.581649], [34.159155, -12.581637], [34.159162, -12.581624], [34.159168, -12.58161], [34.159176, -12.581596], [34.159182, -12.581585], [34.159189, -12.581572], [34.159196, -12.581559], [34.159201, -12.581549], [34.159208, -12.581539], [34.159216, -12.581526], [34.159222, -12.581513], [34.159229, -12.5815], [34.159236, -12.581491], [34.159242, -12.581483], [34.159247, -12.581476], [34.159256, -12.581465], [34.159264, -12.581454], [34.159271, -12.581443], [34.159276, -12.581435], [34.159282, -12.581422], [34.159287, -12.581409], [34.159294, -12.581396], [34.159301, -12.581383], [34.159309, -12.581371], [34.159318, -12.581358], [34.159325, -12.581346], [34.159332, -12.581333], [34.159339, -12.58132], [34.159346, -12.581307], [34.15935, -12.581299], [34.159358, -12.581287], [34.159365, -12.581274], [34.159371, -12.581262], [34.159377, -12.58125], [34.159383, -12.581237], [34.159389, -12.581226], [34.159394, -12.581215], [34.1594, -12.581203], [34.159406, -12.581192], [34.159412, -12.581181], [34.159418, -12.581169], [34.159421, -12.58116], [34.159427, -12.581147], [34.159434, -12.581135], [34.159442, -12.581121], [34.15945, -12.581108], [34.159457, -12.581095], [34.159464, -12.581084], [34.159472, -12.581073], [34.159478, -12.581066], [34.159485, -12.581055], [34.159493, -12.581042], [34.1595, -12.58103], [34.159507, -12.581019], [34.159511, -12.581011], [34.159518, -12.580999], [34.159523, -12.580987], [34.15953, -12.580975], [34.159538, -12.580962], [34.159545, -12.580949], [34.159556, -12.580932], [34.15956, -12.580924], [34.159566, -12.580911], [34.159573, -12.580898], [34.159581, -12.580886], [34.159589, -12.580874], [34.159597, -12.580862], [34.159603, -12.580849], [34.159607, -12.58084], [34.159612, -12.580829], [34.15962, -12.580813], [34.159627, -12.580801], [34.159633, -12.580789], [34.15964, -12.580777], [34.159648, -12.580764], [34.159654, -12.580752], [34.15966, -12.58074], [34.159668, -12.580725], [34.159674, -12.580716], [34.159679, -12.580708], [34.159686, -12.580695], [34.159692, -12.580682], [34.159697, -12.580669], [34.159704, -12.580656], [34.159711, -12.580644], [34.159716, -12.580632], [34.159721, -12.58062], [34.159727, -12.580608], [34.159731, -12.5806], [34.159738, -12.580587], [34.159744, -12.580578], [34.159749, -12.580569], [34.159753, -12.58056], [34.159759, -12.580547], [34.159765, -12.580535], [34.159771, -12.580522], [34.159778, -12.580512], [34.159784, -12.580502], [34.15979, -12.580491], [34.159795, -12.580482], [34.159799, -12.580471], [34.159806, -12.580459], [34.159812, -12.58045], [34.159819, -12.58044], [34.159827, -12.580428], [34.159834, -12.580415], [34.159841, -12.580403], [34.159848, -12.580392], [34.159855, -12.58038], [34.159862, -12.580367], [34.159869, -12.580355], [34.159876, -12.580343], [34.159883, -12.580331], [34.15989, -12.580319], [34.159897, -12.580307], [34.159905, -12.580296], [34.159911, -12.580285], [34.159917, -12.580271], [34.159922, -12.580262], [34.159928, -12.580251], [34.159933, -12.580243], [34.159938, -12.580231], [34.159945, -12.580219], [34.159951, -12.580208], [34.159958, -12.580197], [34.159963, -12.580186], [34.15997, -12.580174], [34.159977, -12.580164], [34.159983, -12.580154], [34.159988, -12.580145], [34.159995, -12.580133], [34.16, -12.580122], [34.160006, -12.58011], [34.160012, -12.5801], [34.160018, -12.580089], [34.160024, -12.580077], [34.160029, -12.580069], [34.160034, -12.580059], [34.160039, -12.580045], [34.160043, -12.580033], [34.160049, -12.580023], [34.160055, -12.580014], [34.160062, -12.580004], [34.160068, -12.579992], [34.160073, -12.57998], [34.16008, -12.579968], [34.160088, -12.579956], [34.160094, -12.579945], [34.160102, -12.579931], [34.160109, -12.579919], [34.160116, -12.579908], [34.160123, -12.579896], [34.160131, -12.579885], [34.160138, -12.579873], [34.160144, -12.579861], [34.160151, -12.579845], [34.160143, -12.57984], [34.160133, -12.579838], [34.160123, -12.579842], [34.160105, -12.579845], [34.160088, -12.579847], [34.160072, -12.579849], [34.160055, -12.579851], [34.160033, -12.57985], [34.160024, -12.579849], [34.16001, -12.579849], [34.159995, -12.579848], [34.159981, -12.579847], [34.159968, -12.579845], [34.159954, -12.579843], [34.159941, -12.579841], [34.159928, -12.579838], [34.159914, -12.579835], [34.159901, -12.579833], [34.159889, -12.579831], [34.159879, -12.579829], [34.159866, -12.579827], [34.159851, -12.579824], [34.159841, -12.579822], [34.159832, -12.57982], [34.159817, -12.579816], [34.159803, -12.579813], [34.159789, -12.579809], [34.159776, -12.579806], [34.159763, -12.579803], [34.159751, -12.5798], [34.159734, -12.579797], [34.159718, -12.579795], [34.159706, -12.579793], [34.159692, -12.579791], [34.159678, -12.57979], [34.159664, -12.579789], [34.159649, -12.579787], [34.159637, -12.579786], [34.159623, -12.579784], [34.159611, -12.579783], [34.159599, -12.579782], [34.159588, -12.579781], [34.159574, -12.579779], [34.159557, -12.579777], [34.159547, -12.579777], [34.159534, -12.579777], [34.159521, -12.579776], [34.159511, -12.579775], [34.159497, -12.579775], [34.159483, -12.579773], [34.15947, -12.579771], [34.159457, -12.579769], [34.159444, -12.579767], [34.159435, -12.579766], [34.159422, -12.579763], [34.159409, -12.579762], [34.159395, -12.57976], [34.159383, -12.579758], [34.159372, -12.579755], [34.159362, -12.579754], [34.159349, -12.579752], [34.159336, -12.579751], [34.159322, -12.57975], [34.159308, -12.579748], [34.159296, -12.579747], [34.159283, -12.579746], [34.159264, -12.579746], [34.159248, -12.579744], [34.159234, -12.579743], [34.159221, -12.579743], [34.159206, -12.579743], [34.159193, -12.579742], [34.15918, -12.579742], [34.159161, -12.579741], [34.159152, -12.579741], [34.159141, -12.579741], [34.159129, -12.579741], [34.159114, -12.579741], [34.1591, -12.579741], [34.159086, -12.579741], [34.159072, -12.579742], [34.159057, -12.579742], [34.159047, -12.579743], [34.159031, -12.579745], [34.15902, -12.579746], [34.159005, -12.579746], [34.158992, -12.579747], [34.158979, -12.579746], [34.158966, -12.579745], [34.158953, -12.579745], [34.158941, -12.579746], [34.158931, -12.579746], [34.158917, -12.579748], [34.158903, -12.57975], [34.158888, -12.579752], [34.158874, -12.579755], [34.158864, -12.579756], [34.158848, -12.579758], [34.158835, -12.579762], [34.158826, -12.579764], [34.158813, -12.579766], [34.158799, -12.579768], [34.158783, -12.57977], [34.158769, -12.579771], [34.158751, -12.579773], [34.158737, -12.579775], [34.158723, -12.579776], [34.158709, -12.579778], [34.158694, -12.579778], [34.15868, -12.579778], [34.158666, -12.579779], [34.158649, -12.579778], [34.158637, -12.57978], [34.158625, -12.57978], [34.158612, -12.579781], [34.158602, -12.579782], [34.158588, -12.579784], [34.158574, -12.579785], [34.15856, -12.579785], [34.158548, -12.579787], [34.158535, -12.57979], [34.158522, -12.579792], [34.158508, -12.579794], [34.158495, -12.579797], [34.158484, -12.579799], [34.158472, -12.579803], [34.158459, -12.579807], [34.158449, -12.57981], [34.158439, -12.579815], [34.158425, -12.57982], [34.15841, -12.579824], [34.158392, -12.57983], [34.158383, -12.579832], [34.158369, -12.579836], [34.158357, -12.57984], [34.15834, -12.579845], [34.158328, -12.579849], [34.158314, -12.579855], [34.158302, -12.579859], [34.15829, -12.579865], [34.158278, -12.57987], [34.158266, -12.579875], [34.158251, -12.579881], [34.15824, -12.579884], [34.158231, -12.579888], [34.158218, -12.579893], [34.158205, -12.579898], [34.158192, -12.579904], [34.158178, -12.579909], [34.158167, -12.579915], [34.158153, -12.579921], [34.158141, -12.579925], [34.158132, -12.579929], [34.158119, -12.579933], [34.158105, -12.579937], [34.158091, -12.57994], [34.158079, -12.579944], [34.158067, -12.579951], [34.158059, -12.57996], [34.158055, -12.579968], [34.15805, -12.579982], [34.158049, -12.579992], [34.158048, -12.580002], [34.158049, -12.580014], [34.158053, -12.580022], [34.15806, -12.580037], [34.158067, -12.580053], [34.158071, -12.580063], [34.158078, -12.580079], [34.158084, -12.580092], [34.15809, -12.580104], [34.158096, -12.580116], [34.1581, -12.580129], [34.158103, -12.580141], [34.158111, -12.580158], [34.158115, -12.580169], [34.158119, -12.580178], [34.158123, -12.580187], [34.158128, -12.580199], [34.158135, -12.580211], [34.158141, -12.580224], [34.158145, -12.580237], [34.158149, -12.580252], [34.158152, -12.580262], [34.158155, -12.580271], [34.15816, -12.580285], [34.158165, -12.580297], [34.15817, -12.580311], [34.158175, -12.580324], [34.158177, -12.580336], [34.158181, -12.580348], [34.158184, -12.580356], [34.158188, -12.580367], [34.158193, -12.580381], [34.158198, -12.580394], [34.158203, -12.580407], [34.158207, -12.580419], [34.158212, -12.580432], [34.158217, -12.580443], [34.158221, -12.580452], [34.158227, -12.580464], [34.158232, -12.580476], [34.158238, -12.580489], [34.158242, -12.580501], [34.158248, -12.580514], [34.158254, -12.580527], [34.158258, -12.580539], [34.158264, -12.580549], [34.158272, -12.580559], [34.158277, -12.580568], [34.158282, -12.580578], [34.158289, -12.580591], [34.158293, -12.580602], [34.158299, -12.580614], [34.158304, -12.580626], [34.158309, -12.580634], [34.158314, -12.580647], [34.158318, -12.58066], [34.158322, -12.580672], [34.158328, -12.580683], [34.158333, -12.580693], [34.158337, -12.580704], [34.158341, -12.580715], [34.158345, -12.580725], [34.15835, -12.580739], [34.158354, -12.580751], [34.15836, -12.580764], [34.158364, -12.580773], [34.158368, -12.580785], [34.158373, -12.580797], [34.158379, -12.580808], [34.158384, -12.58082], [34.158389, -12.580832], [34.158394, -12.580844], [34.158398, -12.580852], [34.158401, -12.580865], [34.158406, -12.580877], [34.158413, -12.58089], [34.158419, -12.580903], [34.158427, -12.580915], [34.158432, -12.580925], [34.158438, -12.580941], [34.158444, -12.580958], [34.15845, -12.58097], [34.158456, -12.580983], [34.158461, -12.580996], [34.158467, -12.58101], [34.158471, -12.581021], [34.158476, -12.581035], [34.158481, -12.581046], [34.158485, -12.581055], [34.15849, -12.581066], [34.158496, -12.581079], [34.158501, -12.581091], [34.158507, -12.581104], [34.158511, -12.581112], [34.158519, -12.581128], [34.158525, -12.581137], [34.15853, -12.58115], [34.158535, -12.581163], [34.158538, -12.581174], [34.158541, -12.581186], [34.158545, -12.581198], [34.158549, -12.58121], [34.158554, -12.581222], [34.15856, -12.581234], [34.158564, -12.581242], [34.158571, -12.581258], [34.158576, -12.581267], [34.158583, -12.58128], [34.158588, -12.581293], [34.158591, -12.581302], [34.158595, -12.581312], [34.1586, -12.581324], [34.158604, -12.581336], [34.158611, -12.58135], [34.158619, -12.581364], [34.158624, -12.581377], [34.158629, -12.581388], [34.158634, -12.581402], [34.158638, -12.581412], [34.158643, -12.581424], [34.158648, -12.581435], [34.158652, -12.581449], [34.158657, -12.581461], [34.158663, -12.581472], [34.158667, -12.581484], [34.158671, -12.581493], [34.158677, -12.581506], [34.15868, -12.581518], [34.158686, -12.581531], [34.158692, -12.581543], [34.158696, -12.581555], [34.1587, -12.581563], [34.158706, -12.581575], [34.15871, -12.581585], [34.158716, -12.581596], [34.158727, -12.581614], [34.158733, -12.581625], [34.158736, -12.581634], [34.158743, -12.581648], [34.158747, -12.581658], [34.158753, -12.581676], [34.158759, -12.58169], [34.158765, -12.581706], [34.15877, -12.581717], [34.158775, -12.581728], [34.158781, -12.581739], [34.158786, -12.581749], [34.158793, -12.581767], [34.158798, -12.581779], [34.158803, -12.58179], [34.158808, -12.581802], [34.158815, -12.581814], [34.158822, -12.581827], [34.158828, -12.581839], [34.158833, -12.581851], [34.158837, -12.58186], [34.158842, -12.581873], [34.158847, -12.581887], [34.158852, -12.581899], [34.158857, -12.581913], [34.158861, -12.581925], [34.158864, -12.581936], [34.158866, -12.581947], [34.158869, -12.58196], [34.158873, -12.581974], [34.158879, -12.581987], [34.158883, -12.581999], [34.158888, -12.582011], [34.158893, -12.582021], [34.158899, -12.582033], [34.158904, -12.582044], [34.15891, -12.582056], [34.158921, -12.582058], [34.158921, -12.582044], [34.158919, -12.58205]]]}}</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-10-19 12:13</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>DCGL-1791274033878-L259IP9X</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LP08012</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>N41</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Clay Loam</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1.503</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 391, "area_m2": 15026.9921875, "area_ha": 1.50269921875, "perimeter_m": 552.1095597890738, "survey_distance_m": 543.3571545267127, "best_accuracy_m": 3, "worst_accuracy_m": 3.884000062942505, "average_accuracy_m": 3.0221381120364685, "survey_started": "2026-10-06T08:00:13.928Z", "survey_completed": "2026-10-06T08:07:13.840Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.160477, -12.582254], [34.160471, -12.582246], [34.160469, -12.582232], [34.160471, -12.582212], [34.160476, -12.582188], [34.160479, -12.582171], [34.160491, -12.582148], [34.160498, -12.582132], [34.160503, -12.582121], [34.160509, -12.582109], [34.160516, -12.582096], [34.160524, -12.582088], [34.160532, -12.582079], [34.16054, -12.582069], [34.160545, -12.582062], [34.160555, -12.582046], [34.160561, -12.582032], [34.160563, -12.582017], [34.160566, -12.582004], [34.160571, -12.581992], [34.160578, -12.58198], [34.160588, -12.581965], [34.160594, -12.581953], [34.1606, -12.581942], [34.160607, -12.58193], [34.160613, -12.58192], [34.160618, -12.581909], [34.160622, -12.581901], [34.160629, -12.581888], [34.160634, -12.581877], [34.160638, -12.581868], [34.160644, -12.581856], [34.160652, -12.581843], [34.160658, -12.581832], [34.160665, -12.581821], [34.160672, -12.581811], [34.160678, -12.581802], [34.160685, -12.581789], [34.160694, -12.581773], [34.1607, -12.581761], [34.160705, -12.58175], [34.16071, -12.581739], [34.160716, -12.581728], [34.160723, -12.581718], [34.160729, -12.581706], [34.160735, -12.581695], [34.160741, -12.581683], [34.160748, -12.581672], [34.160752, -12.581664], [34.160757, -12.581653], [34.160764, -12.581642], [34.160771, -12.581632], [34.160776, -12.581622], [34.160781, -12.581611], [34.160787, -12.581602], [34.160792, -12.58159], [34.160798, -12.581579], [34.160805, -12.581566], [34.160811, -12.581557], [34.160815, -12.581548], [34.160821, -12.581537], [34.160828, -12.581526], [34.160834, -12.581516], [34.16084, -12.581506], [34.160844, -12.581499], [34.160851, -12.581486], [34.160858, -12.581475], [34.160862, -12.581465], [34.160868, -12.581455], [34.160873, -12.581446], [34.160878, -12.581434], [34.160881, -12.581423], [34.160885, -12.581412], [34.160891, -12.5814], [34.160896, -12.581391], [34.160901, -12.58138], [34.160906, -12.58137], [34.16091, -12.581361], [34.160917, -12.581349], [34.160921, -12.58134], [34.160929, -12.581328], [34.16094, -12.581314], [34.160947, -12.581307], [34.160952, -12.581298], [34.160957, -12.58129], [34.160963, -12.581281], [34.16097, -12.58127], [34.160973, -12.581261], [34.160978, -12.581252], [34.160982, -12.581235], [34.160987, -12.581224], [34.160992, -12.581212], [34.160996, -12.581203], [34.161, -12.581193], [34.161005, -12.581183], [34.161011, -12.581172], [34.161017, -12.581162], [34.161025, -12.581153], [34.161031, -12.581143], [34.161037, -12.581133], [34.161045, -12.581124], [34.161052, -12.581115], [34.161059, -12.581105], [34.161064, -12.581095], [34.161069, -12.581084], [34.161074, -12.581073], [34.161081, -12.58106], [34.161086, -12.581052], [34.161097, -12.581036], [34.161104, -12.581024], [34.161111, -12.581012], [34.161117, -12.581001], [34.161125, -12.580988], [34.161131, -12.580978], [34.161138, -12.580967], [34.161143, -12.580956], [34.161149, -12.580945], [34.161154, -12.580936], [34.161159, -12.580927], [34.161164, -12.580916], [34.16117, -12.580907], [34.161174, -12.580898], [34.161178, -12.580888], [34.161183, -12.58088], [34.161188, -12.580871], [34.161193, -12.580863], [34.161198, -12.580854], [34.161203, -12.580845], [34.161208, -12.580836], [34.161213, -12.580827], [34.161219, -12.580816], [34.161226, -12.580807], [34.161233, -12.580798], [34.161238, -12.580789], [34.161244, -12.580778], [34.16125, -12.580765], [34.161257, -12.580753], [34.161265, -12.58074], [34.161269, -12.580729], [34.161276, -12.580718], [34.161282, -12.580709], [34.161289, -12.580697], [34.161294, -12.58069], [34.161301, -12.580682], [34.161312, -12.58068], [34.161323, -12.580686], [34.161331, -12.580699], [34.161337, -12.580708], [34.161345, -12.580719], [34.161353, -12.580731], [34.16136, -12.580744], [34.161366, -12.580755], [34.161373, -12.580764], [34.161378, -12.580772], [34.161384, -12.58078], [34.161391, -12.58079], [34.161397, -12.580797], [34.161405, -12.580806], [34.161414, -12.580815], [34.161422, -12.580823], [34.161432, -12.580833], [34.161441, -12.580842], [34.161449, -12.580851], [34.161458, -12.580865], [34.161469, -12.580877], [34.161476, -12.580885], [34.161487, -12.580901], [34.161492, -12.580911], [34.161497, -12.580919], [34.161508, -12.580933], [34.161518, -12.580945], [34.16153, -12.580956], [34.161536, -12.580967], [34.161541, -12.580977], [34.161546, -12.580986], [34.16155, -12.580996], [34.161557, -12.581007], [34.161562, -12.581015], [34.16157, -12.581027], [34.161577, -12.581038], [34.161583, -12.581048], [34.16159, -12.581061], [34.161597, -12.581072], [34.161603, -12.581081], [34.161608, -12.581091], [34.161612, -12.581099], [34.161614, -12.581109], [34.161616, -12.581119], [34.161621, -12.581128], [34.161628, -12.58114], [34.161636, -12.581149], [34.161642, -12.581156], [34.16165, -12.581167], [34.161656, -12.581176], [34.161662, -12.581185], [34.16167, -12.581195], [34.161676, -12.581203], [34.161683, -12.581212], [34.16169, -12.581222], [34.161695, -12.581231], [34.1617, -12.581242], [34.161704, -12.581251], [34.161709, -12.58126], [34.161714, -12.58127], [34.161716, -12.58128], [34.161722, -12.58129], [34.161728, -12.581299], [34.161732, -12.581308], [34.161736, -12.581318], [34.16174, -12.581329], [34.161745, -12.581339], [34.161749, -12.581348], [34.161755, -12.58136], [34.161759, -12.581373], [34.161763, -12.581382], [34.161768, -12.581392], [34.161773, -12.581402], [34.16178, -12.581414], [34.161784, -12.581427], [34.161788, -12.581438], [34.161792, -12.581448], [34.161796, -12.581459], [34.161802, -12.581474], [34.161807, -12.581487], [34.161811, -12.581499], [34.161814, -12.58151], [34.161816, -12.581521], [34.161821, -12.581535], [34.161826, -12.581551], [34.16183, -12.581564], [34.161836, -12.581576], [34.161841, -12.581589], [34.161845, -12.5816], [34.16185, -12.581611], [34.161856, -12.581619], [34.161863, -12.58163], [34.161866, -12.58164], [34.16187, -12.581652], [34.161874, -12.581667], [34.161879, -12.581678], [34.161883, -12.581689], [34.161886, -12.5817], [34.161889, -12.581711], [34.161894, -12.581719], [34.161899, -12.581731], [34.161902, -12.581741], [34.161904, -12.58175], [34.161906, -12.58176], [34.16191, -12.58177], [34.161914, -12.58178], [34.161918, -12.58179], [34.16192, -12.5818], [34.161922, -12.581812], [34.16193, -12.581822], [34.161936, -12.581831], [34.161943, -12.581844], [34.161949, -12.581856], [34.161956, -12.581864], [34.161964, -12.581875], [34.16197, -12.581885], [34.161977, -12.581893], [34.161984, -12.581904], [34.161994, -12.581922], [34.161996, -12.581933], [34.161996, -12.581946], [34.161997, -12.58196], [34.161984, -12.581969], [34.161974, -12.581967], [34.161959, -12.581964], [34.161944, -12.581962], [34.161929, -12.581959], [34.161916, -12.581957], [34.161906, -12.581955], [34.161891, -12.581954], [34.161878, -12.581954], [34.161866, -12.581957], [34.161853, -12.581959], [34.161841, -12.581961], [34.161829, -12.581963], [34.161818, -12.581964], [34.161803, -12.581967], [34.161791, -12.58197], [34.161778, -12.581973], [34.161768, -12.581976], [34.161755, -12.581981], [34.161742, -12.581985], [34.161728, -12.581988], [34.161713, -12.581993], [34.161697, -12.581996], [34.161685, -12.581999], [34.161671, -12.582003], [34.161658, -12.582009], [34.161643, -12.582013], [34.161629, -12.582016], [34.161613, -12.582022], [34.161602, -12.582026], [34.16159, -12.58203], [34.16158, -12.582032], [34.161566, -12.582034], [34.161552, -12.582035], [34.16154, -12.582038], [34.161528, -12.58204], [34.161515, -12.582043], [34.161505, -12.582045], [34.161491, -12.582049], [34.161477, -12.582055], [34.161464, -12.582058], [34.161451, -12.582061], [34.161439, -12.582064], [34.161428, -12.582067], [34.161418, -12.58207], [34.161408, -12.582071], [34.161392, -12.582075], [34.161378, -12.582077], [34.161365, -12.58208], [34.161352, -12.582082], [34.161339, -12.582084], [34.161327, -12.582087], [34.161317, -12.58209], [34.161303, -12.582093], [34.161288, -12.582096], [34.16127, -12.5821], [34.161257, -12.582103], [34.161246, -12.582105], [34.161231, -12.582108], [34.161212, -12.582111], [34.161194, -12.582115], [34.161183, -12.582119], [34.16117, -12.582122], [34.161157, -12.582124], [34.161145, -12.582127], [34.161133, -12.582129], [34.161119, -12.58213], [34.161108, -12.582134], [34.161098, -12.582137], [34.161085, -12.58214], [34.161072, -12.582142], [34.16106, -12.582145], [34.161048, -12.582147], [34.161036, -12.58215], [34.161024, -12.582152], [34.16101, -12.582155], [34.160998, -12.582159], [34.160986, -12.582163], [34.160973, -12.582166], [34.16096, -12.582169], [34.160949, -12.582171], [34.160927, -12.582174], [34.160915, -12.582177], [34.160902, -12.582179], [34.160886, -12.582181], [34.160873, -12.582183], [34.160859, -12.582186], [34.160845, -12.582189], [34.160832, -12.58219], [34.160816, -12.582193], [34.160804, -12.582195], [34.160791, -12.582198], [34.160779, -12.582201], [34.160769, -12.582203], [34.160754, -12.582208], [34.160741, -12.582211], [34.160729, -12.582212], [34.160716, -12.582213], [34.160703, -12.582215], [34.160693, -12.582216], [34.160681, -12.58222], [34.160668, -12.582223], [34.160653, -12.582227], [34.160642, -12.58223], [34.160629, -12.582234], [34.160617, -12.582237], [34.160607, -12.582239], [34.160594, -12.582243], [34.160581, -12.582246], [34.160569, -12.582249], [34.160556, -12.582251], [34.160542, -12.582253], [34.160533, -12.582254], [34.160519, -12.582257], [34.16051, -12.582259], [34.160495, -12.582261], [34.160481, -12.582263], [34.160467, -12.582266], [34.160452, -12.582268], [34.160439, -12.582271], [34.160424, -12.582272], [34.160415, -12.582273], [34.160403, -12.582274], [34.16039, -12.582275], [34.1604, -12.582275], [34.160477, -12.582254]]]}}</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-10-19 12:13</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
